--- a/data/daily/2026-10/2026-10-20.xlsx
+++ b/data/daily/2026-10/2026-10-20.xlsx
@@ -1218,7 +1218,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1293,7 +1293,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="361950" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1343,7 +1343,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1368,7 +1368,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1473,7 +1473,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1548,7 +1548,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="990600" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1598,7 +1598,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +1623,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2084,33 +2084,29 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16309</v>
+        <v>16312</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로가 풀리고 몸이 한결 가벼워짐</t>
+          <t>피로 회복 및 체력 증진 — 섭취 후 기운이 나고 피로 회복 및 컨디션 관리 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>농축 액상과 알약 구성 — 진한 비타민 원액과 알약의 조합으로 영양 보충 가능함</t>
+          <t>실용적인 선물용 추천 — 지인이나 가족에게 마음을 전하기 좋은 실용적인 선물용 제품임</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용 높은 만족도 — 가격 부담이 적고 선물용으로 인기가 높음</t>
+          <t>농축된 고함량 비타민 — 고용량 액상 비타민 원액이 진해 영양 성분을 효과적으로 섭취 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송 기간이 너무 길고 엄청 늦게 도착함</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>비싼 가격 부담 — 피로 회복에 효과는 있으나 가격이 다소 비쌈</t>
-        </is>
-      </c>
+          <t>느리고 지연되는 배송 — 주문 후 상품을 받기까지 배송 시간이 다소 오래 걸림</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2151,21 +2147,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15649</v>
+        <v>15651</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 영양 보충 — 액상과 정제가 함께 있어 필수 영양소를 간편히 챙김</t>
+          <t>섭취와 휴대의 편리함 — 액상과 정제가 함께 들어 있어 1회 복용 및 간편 섭취에 용이함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 깔끔하고 정성스럽게 포장되어 선물하기 좋음</t>
+          <t>고급스러운 포장 디자인 — 꼼꼼하고 예쁜 패키지 포장으로 선물용 만족도가 높음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>피로 완화 효과 — 몸이 피로할 때 먹으면 덜 피곤하고 만족스러움</t>
+          <t>피로 시 체력 충전 효과 — 장거리 활동이나 피로 시 간편하게 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2214,17 +2210,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 활력 증진 — 섭취 후 피로감이 줄고 생기 넘치는 하루를 보냄</t>
+          <t>넉넉한 용량 구성 — 30개입 구성으로 넉넉하게 오랜 기간 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>넉넉한 대용량 구성 — 30개입 구성이라 온 가족이 나눠 먹거나 오래 먹기 좋음</t>
+          <t>피로 개선 및 활력 증진 — 섭취 후 피로감이 줄고 하루를 활기차게 보낼 수 있음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>감동적인 선물 포장 — 포장이 예쁘고 고급스러워 생일 선물용으로 제격임</t>
+          <t>감동을 주는 고급 포장 — 선물용 패키지 포장이 이쁘고 성의 있게 전달됨</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2273,22 +2269,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 과일맛 젤리 — 거부감 없는 과일맛 젤리 형태라 간식처럼 섭취함</t>
+          <t>맛있는 과일맛 젤리 제형 — 거부감 없이 맛있는 과일 맛 젤리 형태로 간식처럼 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>물 없이 섭취 가능 — 바쁜 아침에도 물 없이 씹어서 간편하게 챙김</t>
+          <t>물 없이 간편한 섭취 — 바쁜 아침에도 물 없이 씹어서 간편하게 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>어린이 안전캡 적용 — 안전캡이 씌워져 있어 아이가 있는 집에서도 안심함</t>
+          <t>빠른 배송과 안전 용기 — 배송이 빠르고 아이들이 있는 집에서도 안심할 수 있는 안전캡 용기임</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>일일 섭취량 제한 — 맛있어서 더 먹고 싶으나 정해진 양만 먹어야 해서 아쉬움</t>
+          <t>섭취량 조절의 어려움 — 너무 맛있어서 하루 정해진 권장량 이상 먹게 됨</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2336,18 +2332,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>확실한 체력 체감 — 꾸준히 먹으면 덜 지치고 피로로 인한 증상이 개선됨</t>
+          <t>빠른 피로 회복 효과 — 섭취 시 혓바늘 완화 등 체력 회복과 피로 개선에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>할인 및 증정 혜택 — 세일 및 추가 증정 이벤트로 가성비 있게 구매함</t>
+          <t>할인을 통한 가성비 구매 — 할인 이벤트 및 증정 혜택으로 저렴하게 구매함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>짧은 유통기한 — 제품의 유통기한 및 소비기한이 생각보다 짧음</t>
+          <t>아쉬운 짧은 소비기한 — 할인 가격 대비 제품의 남은 유통기한이 생각보다 짧음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2391,21 +2387,21 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>효과적인 피로 회복 — 환절기 컨디션 관리 및 일상 피로 해소에 도움 됨</t>
+          <t>피로 회복 체감 효과 — 섭취 후 피로가 잘 풀리고 환절기 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 먹기 편하고 챙겨 다니기 용이한 제형임</t>
+          <t>간편한 휴대성 및 복용 — 먹기 편하고 휴대하기 좋아 일상에서 챙겨 먹기 유용함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>센스 있는 선물 — 품질이 좋고 건강을 챙길 수 있는 기분 좋은 선물임</t>
+          <t>센스 있는 생일 선물 — 품질이 우수하고 부담 없이 선물하기 좋은 제품임</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2415,7 +2411,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2423,53 +2419,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/3252731</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>969</v>
+        <v>1782</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>면역 및 건강 관리 — 감기 초기나 입병 예방 등 건강 관리에 효과적임</t>
+          <t>빠른 피로 회복 및 에너지 — 섭취 시 즉각적인 생기와 에너지가 도는 느낌을 받음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>합리적인 할인 가격 — 할인 행사를 통해 착한 가격으로 구매함</t>
+          <t>고급스러운 패키지 디자인 — 포장이 예쁘고 고급스러워 생일 및 지인 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>매우 빠른 배송 — 주문 후 배송이 매우 속도감 있게 진행됨</t>
+          <t>재미있고 간편한 복용법 — 버튼을 눌러 분말을 섞어 먹는 방식이 신기하고 휴대 및 복용이 편함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 신맛과 쓴맛이 매우 강함</t>
+          <t>쌉쌀한 맛과 사용법 숙지 — 분말 섞일 때 약간의 쌉쌀한 맛이 나며 섭취 방법 숙지가 필요함</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -2478,7 +2474,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2486,60 +2482,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/3252731</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1782</v>
+        <v>970</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>신선한 복용 방식 — 버튼을 눌러 가루를 섞어 먹는 재미와 편리함이 있음</t>
+          <t>감기 및 건강 개선 도움 — 꾸준한 복용으로 감기와 입병 예방 등 건강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>즉각적인 활력 충전 — 마신 후 지친 일상에 생기와 에너지가 돋음</t>
+          <t>착한 가격과 빠른 배송 — 할인가로 저렴하게 구매할 수 있으며 배송이 매우 빠름</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 선물용 패키지 포장이 예쁘고 깔끔함</t>
+          <t>신뢰받는 브랜드 품질 — 고려은단 브랜드 제품이라 원재료를 믿고 꾸준히 구매함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>분말의 쌉쌀한 맛 — 섞여 나오는 노란 가루의 맛이 다소 쌉쌀함</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>섭취 방법 안내 필요 — 가루를 섞는 사용법을 모르면 투명한 액상만 마실 위험 있음</t>
-        </is>
-      </c>
+          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 강한 신맛과 쓴맛이 느껴짐</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -2584,17 +2576,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>간편한 액상 제형 — 마시는 형태로 되어 있어 챙겨 먹기 매우 편함</t>
+          <t>간편한 마시는 액상 제형 — 마시는 액상 형태라 물 없이도 어디서나 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 — 먹고 자면 다음 날 컨디션과 에너지가 확연히 달라짐</t>
+          <t>확실한 컨디션 개선 — 섭취 후 다음 날 피로가 풀리고 에너지가 생김을 체감함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>받는 이의 높은 만족 — 지인이나 어른들에게 센스 있게 선물하기 좋음</t>
+          <t>기분 좋은 건강 선물 — 생일이나 지인 선물용으로 주고받기 유용함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -2639,21 +2631,21 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>상쾌한 피로 해소 — 하루 한 병으로 피로가 사라지고 온종일 힘이 남</t>
+          <t>위생적인 이중 구성 — 액상과 알약이 분리되어 있어 위생적이고 간편하게 함께 먹기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>위생적인 이중 구성 — 액상과 알약이 따로 나뉘어 있어 위생적임</t>
+          <t>빠른 피로 회복 및 활력 — 피곤할 때 섭취 시 하루 종일 기운이 나고 피로가 풀림</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 돌아다니면서도 간편하게 챙겨 먹을 수 있음</t>
+          <t>빠른 배송과 포장 상태 — 포장 상태가 우수하고 빠르게 배송되어 신뢰감이 감</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2698,26 +2690,26 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 거부감 없이 즐길 수 있는 고소한 맛임</t>
+          <t>고소한 미숫가루 맛 — 거부감 없이 고소한 미숫가루 맛으로 아이도 잘 먹음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>소화 및 배변 도움 — 더부룩함이 줄어들고 화장실을 잘 가게 됨</t>
+          <t>소화 및 배변 활동 개선 — 꾸준히 섭취 시 배변 활동에 도움을 받고 소화 기능이 개선됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>풍성한 증정품 — 견과류바 등 알찬 구성품이 함께 제공됨</t>
+          <t>정성스런 포장과 증정품 — 고급스러운 포장과 견과류바 등 푸짐한 사은품 증정으로 구성이 알침</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>이벤트 사은품 누락 — 안내된 기프티콘 증정품이 포함되어 오지 않음</t>
+          <t>사은품 구성 누락 — 안내된 기프티콘 사은품이 누락되어 전달됨</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2726,7 +2718,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2734,66 +2726,62 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45,900원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261016144543_db4a1b51e2064a748811e238969d0330.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>155</v>
+        <v>938</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 소스 맛이 훌륭하며 하나만 먹어도 속이 든든함</t>
+          <t>소화 및 속 편안함 개선 — 식사 후 섭취 시 소화가 잘 되고 배에 가스가 차지 않음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>저렴한 구매 기회 — 할인 이벤트를 통해 가성비 높게 구입함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>숙변 및 변비 완화 — 꾸준히 복용 시 변비 해소 및 숙변 배출에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>착한 가격과 풍성한 사은품 — 할인 가격에 견과류바 등 푸짐한 증정품을 함께 받음</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>오배송 및 구성 오류 — 주문한 품목이 오지 않고 다른 제품으로 중복 배송됨</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>포장 불량 및 터짐 — 포장이 헐렁하여 제품이 터지고 소스가 묻어남</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>다소 자극적인 간 — 생각했던 것보다 간이 세게 느껴짐</t>
-        </is>
-      </c>
+          <t>아쉬운 향과 맛 — 이전 프리미엄 제품에 비해 냄새와 맛이 아쉬움</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2801,62 +2789,66 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>45,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261016144543_db4a1b51e2064a748811e238969d0330.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>937</v>
+        <v>156</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>탁월한 소화 효과 — 식사 후 복용 시 소화가 잘되고 가스 및 변비가 완화됨</t>
+          <t>뛰어난 맛과 포만감 — 다양한 맛이 맛있고 하나만 먹어도 포만감이 오래 유지됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>푸짐한 증정 혜택 — 착한 가격에 넉넉한 사은품까지 함께 전달됨</t>
+          <t>예쁜 사은품 보냉백 — 할인 가격 구성에 더해 디자인이 예쁜 보냉백을 사은품으로 제공함</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>아쉬운 맛과 향 — 기존 프리미엄 제품에 비해 냄새와 맛이 떨어짐</t>
+          <t>오배송 및 미흡한 문의 대응 — 주문한 구성과 다르게 제품이 오배송되고 판매자 문의 응답이 없음</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>교환 및 환불 불가 — 구매 후 교환이나 환불 처리가 불가능함</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>포장 불량으로 인한 터짐 — 비닐 포장이 헐렁하여 팩이 터지고 소스가 새어 나옴</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>다소 강하고 짠 간 — 생각보다 간이 강하여 단독으로 먹기엔 짤 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2864,48 +2856,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>70</v>
+        <v>266</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 다양한 맛 — 닭가슴살이 촉촉하며 다양한 맛이 있어 질리지 않음</t>
+          <t>맛있는 맛과 간식 활용 — 효소가 맛있어서 출출할 때 간식용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지로 빠르게 데워 먹기 편리함</t>
+          <t>고품질 포토카드 구성 — 멤버별 포토카드 퀄리티가 훌륭하고 푸짐한 사은품을 제공함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>신속하고 안전한 배송 — 배송이 빠르고 튼튼하게 포장되어 전달됨</t>
+          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 선물하기 좋을 정도로 포장이 깔끔함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2915,7 +2907,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2923,48 +2915,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>266</v>
+        <v>70</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>맛있는 간식 대용 — 효소 맛이 뛰어나 출출할 때 간식처럼 먹기 좋음</t>
+          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 양념 맛이 훌륭함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>알찬 굿즈 및 사은품 — 포토카드 퀄리티가 높고 단백질바 증정 구성이 좋음</t>
+          <t>간편한 전자레인지 조리 — 전자레인지에 간편하게 데워 먹을 수 있어 편리함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>빠른 배송 및 포장 — 배송이 신속하며 포장이 매우 깔끔하게 옴</t>
+          <t>다양하고 질리지 않는 맛 — 여러 가지 맛과 식감으로 구성되어 질리지 않고 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3013,22 +3005,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 포장과 구성품이 예쁘고 고급스러워 선물용으로 인기 높음</t>
+          <t>고급스럽고 예쁜 패키지 — 포장 패키지와 플리츠백 구성이 고급스러워 개봉 시 기분이 좋아짐</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>맛있는 앰플 제형 — 맛이 좋아 거부감 없이 매일 꾸준히 섭취 가능함</t>
+          <t>거부감 없는 맛있는 맛 — 맛이 좋아 하루 한 병씩 꾸준히 마시기 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>피로 및 탄력 개선 — 피로감이 줄어들고 피부 건강 관리에 기대됨</t>
+          <t>피부 탄력 및 피로 개선 — 꾸준히 섭취 시 피부 탄력 유지와 피로 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>비싼 정가 부담 — 품질은 좋으나 가격이 비싸 할인 시에만 구매하게 됨</t>
+          <t>부담스러운 정가 가격 — 제품 품질은 우수하나 정가가 다소 비싸 할인 시 구매하게 됨</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3076,17 +3068,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>확실한 숙취 개선 — 음주 전후 복용 시 다음 날 두통이 없고 속이 개운함</t>
+          <t>확실한 숙취 완화 효과 — 음주 전후 복용 시 다음 날 두통과 숙취가 확연히 줄어듦</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>편리한 개별 스틱 — 스틱 액상형이라 휴대성이 좋고 물 없이 섭취함</t>
+          <t>간편한 스틱 액상 형태 — 스틱형 액상 포장으로 물 없이 휴대하고 복용하기 편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>예쁜 선물용 세트 — 보라색 패키지 포장이 고급스러워 회식 및 지인 선물로 좋음</t>
+          <t>고급스러운 선물용 구성 — 보라색 선물세트 패키지가 고급스러워 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3135,22 +3127,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 풍미 — 단백질 특유의 비린 맛이 없고 달콤하게 마시기 좋음</t>
+          <t>락토프리로 속 편안함 — 락토프리 유제품이라 마신 후에도 속이 편안하고 부담 없음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 — 유당이 없어 마신 후에도 속이 편안함</t>
+          <t>비린 맛 없는 맛있는 음료 — 단백질 특유의 비린 맛이 없고 맛있는 우유 맛으로 마실 수 있음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>빠른 배송과 증정품 — 배송이 빠르며 에너지바 증정이 만족스러움</t>
+          <t>빠른 배송과 서비스 증정 — 배송이 빠르며 에너지바 및 프로틴바 사은품 증정 혜택이 좋음</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>특정 맛의 느낀점 — 밀크바나나 맛은 개인에 따라 다소 느끼할 수 있음</t>
+          <t>일부 맛의 느껴짐 — 밀크바닐라 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3198,17 +3190,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>음료 같은 맛있는 풍미 — 텁텁하거나 비린 맛없이 진하고 달달한 음료 맛임</t>
+          <t>텁텁함 없는 깔끔한 맛 — 단백질 특유의 텁텁함과 비린 맛이 없어 일반 음료처럼 맛있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>든든한 포만감 — 섭취 시 허기짐이 달래져 간식 대용으로 적합함</t>
+          <t>든든한 포만감 형성 — 간식 땡길 때나 운동 후 섭취 시 은근히 배가 차고 포만감이 높음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>간편한 운동 후 보충 — 운동 후 하나씩 마시며 단백질을 챙기기 편함</t>
+          <t>운동 후 단백질 충전 — 운동 직후 한 팩씩 쉽고 편리하게 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3257,17 +3249,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>풍부한 크런치 토핑 — 토핑이 가득 들어있어 씹는 식감이 우수함</t>
+          <t>풍부하고 바삭한 토핑 — 토핑이 가득 들어 있어 씹는 식감이 좋고 즐겁게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>오래가는 포만감 — 먹고 나면 든든함이 오래 유지되어 식사 대용으로 좋음</t>
+          <t>맹물로도 우수한 맛 — 물만 타서 흔들어 먹어도 충분히 고소하고 달달하여 맛있음</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>물만 타도 뛰어난 맛 — 우유 없이 맹물만 넣어도 텁텁함 없이 달콤하고 맛있음</t>
+          <t>간편한 파우치와 포만감 — 파우치 형태라 휴대하기 편하며 섭취 후 포만감이 오래 유지됨</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3415,12 +3407,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -3472,12 +3464,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3529,12 +3521,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3592,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16309</v>
+        <v>16312</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15649</v>
+        <v>15651</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3414</v>
@@ -3607,19 +3599,19 @@
         <v>129</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>969</v>
+        <v>1782</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1782</v>
+        <v>970</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>8756</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3630,75 +3622,75 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로가 풀리고 몸이 한결 가벼워짐
-농축 액상과 알약 구성 — 진한 비타민 원액과 알약의 조합으로 영양 보충 가능함
-선물용 높은 만족도 — 가격 부담이 적고 선물용으로 인기가 높음</t>
+          <t>피로 회복 및 체력 증진 — 섭취 후 기운이 나고 피로 회복 및 컨디션 관리 효과가 뛰어남
+실용적인 선물용 추천 — 지인이나 가족에게 마음을 전하기 좋은 실용적인 선물용 제품임
+농축된 고함량 비타민 — 고용량 액상 비타민 원액이 진해 영양 성분을 효과적으로 섭취 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 영양 보충 — 액상과 정제가 함께 있어 필수 영양소를 간편히 챙김
-고급스러운 포장 — 패키지가 깔끔하고 정성스럽게 포장되어 선물하기 좋음
-피로 완화 효과 — 몸이 피로할 때 먹으면 덜 피곤하고 만족스러움</t>
+          <t>섭취와 휴대의 편리함 — 액상과 정제가 함께 들어 있어 1회 복용 및 간편 섭취에 용이함
+고급스러운 포장 디자인 — 꼼꼼하고 예쁜 패키지 포장으로 선물용 만족도가 높음
+피로 시 체력 충전 효과 — 장거리 활동이나 피로 시 간편하게 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 활력 증진 — 섭취 후 피로감이 줄고 생기 넘치는 하루를 보냄
-넉넉한 대용량 구성 — 30개입 구성이라 온 가족이 나눠 먹거나 오래 먹기 좋음
-감동적인 선물 포장 — 포장이 예쁘고 고급스러워 생일 선물용으로 제격임</t>
+          <t>넉넉한 용량 구성 — 30개입 구성으로 넉넉하게 오랜 기간 챙겨 먹을 수 있음
+피로 개선 및 활력 증진 — 섭취 후 피로감이 줄고 하루를 활기차게 보낼 수 있음
+감동을 주는 고급 포장 — 선물용 패키지 포장이 이쁘고 성의 있게 전달됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일맛 젤리 — 거부감 없는 과일맛 젤리 형태라 간식처럼 섭취함
-물 없이 섭취 가능 — 바쁜 아침에도 물 없이 씹어서 간편하게 챙김
-어린이 안전캡 적용 — 안전캡이 씌워져 있어 아이가 있는 집에서도 안심함</t>
+          <t>맛있는 과일맛 젤리 제형 — 거부감 없이 맛있는 과일 맛 젤리 형태로 간식처럼 섭취 가능함
+물 없이 간편한 섭취 — 바쁜 아침에도 물 없이 씹어서 간편하게 영양을 챙길 수 있음
+빠른 배송과 안전 용기 — 배송이 빠르고 아이들이 있는 집에서도 안심할 수 있는 안전캡 용기임</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>확실한 체력 체감 — 꾸준히 먹으면 덜 지치고 피로로 인한 증상이 개선됨
-할인 및 증정 혜택 — 세일 및 추가 증정 이벤트로 가성비 있게 구매함</t>
+          <t>빠른 피로 회복 효과 — 섭취 시 혓바늘 완화 등 체력 회복과 피로 개선에 도움 됨
+할인을 통한 가성비 구매 — 할인 이벤트 및 증정 혜택으로 저렴하게 구매함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>효과적인 피로 회복 — 환절기 컨디션 관리 및 일상 피로 해소에 도움 됨
-편리한 휴대성 — 먹기 편하고 챙겨 다니기 용이한 제형임
-센스 있는 선물 — 품질이 좋고 건강을 챙길 수 있는 기분 좋은 선물임</t>
+          <t>피로 회복 체감 효과 — 섭취 후 피로가 잘 풀리고 환절기 컨디션 관리에 도움 됨
+간편한 휴대성 및 복용 — 먹기 편하고 휴대하기 좋아 일상에서 챙겨 먹기 유용함
+센스 있는 생일 선물 — 품질이 우수하고 부담 없이 선물하기 좋은 제품임</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>면역 및 건강 관리 — 감기 초기나 입병 예방 등 건강 관리에 효과적임
-합리적인 할인 가격 — 할인 행사를 통해 착한 가격으로 구매함
-매우 빠른 배송 — 주문 후 배송이 매우 속도감 있게 진행됨</t>
+          <t>빠른 피로 회복 및 에너지 — 섭취 시 즉각적인 생기와 에너지가 도는 느낌을 받음
+고급스러운 패키지 디자인 — 포장이 예쁘고 고급스러워 생일 및 지인 선물용으로 훌륭함
+재미있고 간편한 복용법 — 버튼을 눌러 분말을 섞어 먹는 방식이 신기하고 휴대 및 복용이 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>신선한 복용 방식 — 버튼을 눌러 가루를 섞어 먹는 재미와 편리함이 있음
-즉각적인 활력 충전 — 마신 후 지친 일상에 생기와 에너지가 돋음
-고급스러운 포장 — 선물용 패키지 포장이 예쁘고 깔끔함</t>
+          <t>감기 및 건강 개선 도움 — 꾸준한 복용으로 감기와 입병 예방 등 건강 관리에 도움 됨
+착한 가격과 빠른 배송 — 할인가로 저렴하게 구매할 수 있으며 배송이 매우 빠름
+신뢰받는 브랜드 품질 — 고려은단 브랜드 제품이라 원재료를 믿고 꾸준히 구매함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>간편한 액상 제형 — 마시는 형태로 되어 있어 챙겨 먹기 매우 편함
-확실한 피로 개선 — 먹고 자면 다음 날 컨디션과 에너지가 확연히 달라짐
-받는 이의 높은 만족 — 지인이나 어른들에게 센스 있게 선물하기 좋음</t>
+          <t>간편한 마시는 액상 제형 — 마시는 액상 형태라 물 없이도 어디서나 간편하게 섭취 가능함
+확실한 컨디션 개선 — 섭취 후 다음 날 피로가 풀리고 에너지가 생김을 체감함
+기분 좋은 건강 선물 — 생일이나 지인 선물용으로 주고받기 유용함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>상쾌한 피로 해소 — 하루 한 병으로 피로가 사라지고 온종일 힘이 남
-위생적인 이중 구성 — 액상과 알약이 따로 나뉘어 있어 위생적임
-뛰어난 휴대성 — 돌아다니면서도 간편하게 챙겨 먹을 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>위생적인 이중 구성 — 액상과 알약이 분리되어 있어 위생적이고 간편하게 함께 먹기 좋음
+빠른 피로 회복 및 활력 — 피곤할 때 섭취 시 하루 종일 기운이 나고 피로가 풀림
+빠른 배송과 포장 상태 — 포장 상태가 우수하고 빠르게 배송되어 신뢰감이 감</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3706,32 +3698,30 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송 기간이 너무 길고 엄청 늦게 도착함
-비싼 가격 부담 — 피로 회복에 효과는 있으나 가격이 다소 비쌈</t>
+          <t>느리고 지연되는 배송 — 주문 후 상품을 받기까지 배송 시간이 다소 오래 걸림</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>일일 섭취량 제한 — 맛있어서 더 먹고 싶으나 정해진 양만 먹어야 해서 아쉬움</t>
+          <t>섭취량 조절의 어려움 — 너무 맛있어서 하루 정해진 권장량 이상 먹게 됨</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>짧은 유통기한 — 제품의 유통기한 및 소비기한이 생각보다 짧음</t>
+          <t>아쉬운 짧은 소비기한 — 할인 가격 대비 제품의 남은 유통기한이 생각보다 짧음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 신맛과 쓴맛이 매우 강함</t>
+          <t>쌉쌀한 맛과 사용법 숙지 — 분말 섞일 때 약간의 쌉쌀한 맛이 나며 섭취 방법 숙지가 필요함</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>분말의 쌉쌀한 맛 — 섞여 나오는 노란 가루의 맛이 다소 쌉쌀함
-섭취 방법 안내 필요 — 가루를 섞는 사용법을 모르면 투명한 액상만 마실 위험 있음</t>
+          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 강한 신맛과 쓴맛이 느껴짐</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -3775,12 +3765,12 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -3938,22 +3928,22 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3995,22 +3985,22 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4052,22 +4042,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
-        </is>
-      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -4140,19 +4130,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>155</v>
+        <v>938</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>937</v>
+        <v>156</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>70</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>266</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>757</v>
@@ -4178,70 +4168,71 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 거부감 없이 즐길 수 있는 고소한 맛임
-소화 및 배변 도움 — 더부룩함이 줄어들고 화장실을 잘 가게 됨
-풍성한 증정품 — 견과류바 등 알찬 구성품이 함께 제공됨</t>
+          <t>고소한 미숫가루 맛 — 거부감 없이 고소한 미숫가루 맛으로 아이도 잘 먹음
+소화 및 배변 활동 개선 — 꾸준히 섭취 시 배변 활동에 도움을 받고 소화 기능이 개선됨
+정성스런 포장과 증정품 — 고급스러운 포장과 견과류바 등 푸짐한 사은품 증정으로 구성이 알침</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 소스 맛이 훌륭하며 하나만 먹어도 속이 든든함
-저렴한 구매 기회 — 할인 이벤트를 통해 가성비 높게 구입함</t>
+          <t>소화 및 속 편안함 개선 — 식사 후 섭취 시 소화가 잘 되고 배에 가스가 차지 않음
+숙변 및 변비 완화 — 꾸준히 복용 시 변비 해소 및 숙변 배출에 도움이 됨
+착한 가격과 풍성한 사은품 — 할인 가격에 견과류바 등 푸짐한 증정품을 함께 받음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 소화 효과 — 식사 후 복용 시 소화가 잘되고 가스 및 변비가 완화됨
-푸짐한 증정 혜택 — 착한 가격에 넉넉한 사은품까지 함께 전달됨</t>
+          <t>뛰어난 맛과 포만감 — 다양한 맛이 맛있고 하나만 먹어도 포만감이 오래 유지됨
+예쁜 사은품 보냉백 — 할인 가격 구성에 더해 디자인이 예쁜 보냉백을 사은품으로 제공함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 다양한 맛 — 닭가슴살이 촉촉하며 다양한 맛이 있어 질리지 않음
-간편한 전자레인지 조리 — 전자레인지로 빠르게 데워 먹기 편리함
-신속하고 안전한 배송 — 배송이 빠르고 튼튼하게 포장되어 전달됨</t>
+          <t>맛있는 맛과 간식 활용 — 효소가 맛있어서 출출할 때 간식용으로 먹기 좋음
+고품질 포토카드 구성 — 멤버별 포토카드 퀄리티가 훌륭하고 푸짐한 사은품을 제공함
+빠른 배송과 깔끔한 포장 — 배송이 빠르고 선물하기 좋을 정도로 포장이 깔끔함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 간식 대용 — 효소 맛이 뛰어나 출출할 때 간식처럼 먹기 좋음
-알찬 굿즈 및 사은품 — 포토카드 퀄리티가 높고 단백질바 증정 구성이 좋음
-빠른 배송 및 포장 — 배송이 신속하며 포장이 매우 깔끔하게 옴</t>
+          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 양념 맛이 훌륭함
+간편한 전자레인지 조리 — 전자레인지에 간편하게 데워 먹을 수 있어 편리함
+다양하고 질리지 않는 맛 — 여러 가지 맛과 식감으로 구성되어 질리지 않고 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 포장과 구성품이 예쁘고 고급스러워 선물용으로 인기 높음
-맛있는 앰플 제형 — 맛이 좋아 거부감 없이 매일 꾸준히 섭취 가능함
-피로 및 탄력 개선 — 피로감이 줄어들고 피부 건강 관리에 기대됨</t>
+          <t>고급스럽고 예쁜 패키지 — 포장 패키지와 플리츠백 구성이 고급스러워 개봉 시 기분이 좋아짐
+거부감 없는 맛있는 맛 — 맛이 좋아 하루 한 병씩 꾸준히 마시기 편함
+피부 탄력 및 피로 개선 — 꾸준히 섭취 시 피부 탄력 유지와 피로 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 개선 — 음주 전후 복용 시 다음 날 두통이 없고 속이 개운함
-편리한 개별 스틱 — 스틱 액상형이라 휴대성이 좋고 물 없이 섭취함
-예쁜 선물용 세트 — 보라색 패키지 포장이 고급스러워 회식 및 지인 선물로 좋음</t>
+          <t>확실한 숙취 완화 효과 — 음주 전후 복용 시 다음 날 두통과 숙취가 확연히 줄어듦
+간편한 스틱 액상 형태 — 스틱형 액상 포장으로 물 없이 휴대하고 복용하기 편함
+고급스러운 선물용 구성 — 보라색 선물세트 패키지가 고급스러워 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 풍미 — 단백질 특유의 비린 맛이 없고 달콤하게 마시기 좋음
-속 편한 락토프리 — 유당이 없어 마신 후에도 속이 편안함
-빠른 배송과 증정품 — 배송이 빠르며 에너지바 증정이 만족스러움</t>
+          <t>락토프리로 속 편안함 — 락토프리 유제품이라 마신 후에도 속이 편안하고 부담 없음
+비린 맛 없는 맛있는 음료 — 단백질 특유의 비린 맛이 없고 맛있는 우유 맛으로 마실 수 있음
+빠른 배송과 서비스 증정 — 배송이 빠르며 에너지바 및 프로틴바 사은품 증정 혜택이 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>음료 같은 맛있는 풍미 — 텁텁하거나 비린 맛없이 진하고 달달한 음료 맛임
-든든한 포만감 — 섭취 시 허기짐이 달래져 간식 대용으로 적합함
-간편한 운동 후 보충 — 운동 후 하나씩 마시며 단백질을 챙기기 편함</t>
+          <t>텁텁함 없는 깔끔한 맛 — 단백질 특유의 텁텁함과 비린 맛이 없어 일반 음료처럼 맛있음
+든든한 포만감 형성 — 간식 땡길 때나 운동 후 섭취 시 은근히 배가 차고 포만감이 높음
+운동 후 단백질 충전 — 운동 직후 한 팩씩 쉽고 편리하게 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>풍부한 크런치 토핑 — 토핑이 가득 들어있어 씹는 식감이 우수함
-오래가는 포만감 — 먹고 나면 든든함이 오래 유지되어 식사 대용으로 좋음
-물만 타도 뛰어난 맛 — 우유 없이 맹물만 넣어도 텁텁함 없이 달콤하고 맛있음</t>
+          <t>풍부하고 바삭한 토핑 — 토핑이 가득 들어 있어 씹는 식감이 좋고 즐겁게 먹을 수 있음
+맹물로도 우수한 맛 — 물만 타서 흔들어 먹어도 충분히 고소하고 달달하여 맛있음
+간편한 파우치와 포만감 — 파우치 형태라 휴대하기 편하며 섭취 후 포만감이 오래 유지됨</t>
         </is>
       </c>
     </row>
@@ -4253,33 +4244,32 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>이벤트 사은품 누락 — 안내된 기프티콘 증정품이 포함되어 오지 않음</t>
+          <t>사은품 구성 누락 — 안내된 기프티콘 사은품이 누락되어 전달됨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>오배송 및 구성 오류 — 주문한 품목이 오지 않고 다른 제품으로 중복 배송됨
-포장 불량 및 터짐 — 포장이 헐렁하여 제품이 터지고 소스가 묻어남
-다소 자극적인 간 — 생각했던 것보다 간이 세게 느껴짐</t>
+          <t>아쉬운 향과 맛 — 이전 프리미엄 제품에 비해 냄새와 맛이 아쉬움</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 맛과 향 — 기존 프리미엄 제품에 비해 냄새와 맛이 떨어짐
-교환 및 환불 불가 — 구매 후 교환이나 환불 처리가 불가능함</t>
+          <t>오배송 및 미흡한 문의 대응 — 주문한 구성과 다르게 제품이 오배송되고 판매자 문의 응답이 없음
+포장 불량으로 인한 터짐 — 비닐 포장이 헐렁하여 팩이 터지고 소스가 새어 나옴
+다소 강하고 짠 간 — 생각보다 간이 강하여 단독으로 먹기엔 짤 수 있음</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>비싼 정가 부담 — 품질은 좋으나 가격이 비싸 할인 시에만 구매하게 됨</t>
+          <t>부담스러운 정가 가격 — 제품 품질은 우수하나 정가가 다소 비싸 할인 시 구매하게 됨</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>특정 맛의 느낀점 — 밀크바나나 맛은 개인에 따라 다소 느끼할 수 있음</t>
+          <t>일부 맛의 느껴짐 — 밀크바닐라 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4298,22 +4288,22 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>23,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>45,900원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>23,900원</t>
-        </is>
-      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>33,000원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4528,7 +4518,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4536,54 +4526,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영진 비타민D 1000IU 아연 츄어블 12정</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>영진약품</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314184&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260310/KC1U8zhHXeeJFHKQB2Hr286314184_00_01KC1U8zhHXeeJFHKQB2Hr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260928/FbxeJLkidw2iKLnCp7Pe033991021_00_00FbxeJLkidw2iKLnCp7Pe.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>299</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 천원이라는 부담 없는 가격으로 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>간편한 츄어블 형태 — 씹어 먹는 타입이라 간편하게 건강을 챙김</t>
-        </is>
-      </c>
+          <t>무난한 체중 관리 활용 — 다이어트 보조용으로 부담 없이 꾸준히 복용하기 무난함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>카페인 민감자 주의 — 카페인 성분이 포함되어 체질에 따라 잘 맞지 않을 수 있음</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>미미한 다이어트 효과 — 체감되는 뚜렷한 체중 감량 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4591,7 +4585,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4601,36 +4595,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>7458</v>
+        <v>365</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격 부담이 없어 꾸준히 구매하기 좋음</t>
+          <t>아주 작은 알약 크기 — 정제 크기가 매우 작아 목넘김이 편하고 삼키기 쉬움</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>높은 매장 접근성 — 다이소에서 쉽게 구경하고 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>가성비 뛰어난 고함량 — 다이소 특성상 저렴한 가격 대비 영양 함량이 우수함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>높은 브랜드 신뢰도 — 대웅제약 브랜드 제품이라 안심하고 믿고 구매함</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -4638,7 +4636,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4646,66 +4644,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2929</v>
+        <v>7010</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>커피 대용으로 용이 — 일반 커피와 맛이 유사하여 부담 없이 마심</t>
+          <t>훌륭한 가성비 영양제 — 저렴한 가격에 좋은 품질을 갖추어 꾸준히 구매하기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>배변 활동 도움 — 섭취 후 화장실을 잘 가도록 도와줌</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>편리한 개별 포장 — 한 포씩 개별 포장되어 챙겨 먹기 간편함</t>
-        </is>
-      </c>
+          <t>피로 개선 체감 효과 — 복용을 중단하면 바로 피로감을 느낄 정도로 효능 체감이 확실함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>아쉬운 맛 체감 — 다이어트용이라 맛에 대한 기대는 안 하는 것이 좋음</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>적은 포장 수량 — 10포 구성이라 금방 소진되어 자주 사야 함</t>
-        </is>
-      </c>
+          <t>둔감한 효능 체감 — 사람에 따라 복용 후 뚜렷한 효과를 체감하기 어려울 수 있음</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4713,7 +4703,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4723,33 +4713,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>7006</v>
+        <v>6817</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>재구매율 높은 가성비 — 가격 대비 품질이 뛰어나 꾸준히 구매함</t>
+          <t>부담 없는 저렴한 가격 — 가성비가 매우 뛰어나라 저렴하게 오메가3를 챙길 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>피로 체감 효과 — 복용하지 않으면 피로감이 느껴질 정도로 도움 됨</t>
+          <t>부담 없는 섭취 편의성 — 캡슐 섭취 시 부담이 없어 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4760,7 +4750,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4768,7 +4758,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4778,36 +4768,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000280&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/1DUhwiP05cMCEONDxu7B600000280_00_011DUhwiP05cMCEONDxu7B.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>6816</v>
+        <v>329</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 착한 가격에 오메가3를 구매할 수 있음</t>
+          <t>소용량 포장의 휴대성 — 6일분 소용량 구성으로 단기 피로 시나 여행용으로 챙기기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>부담 없는 알약 섭취 — 하루 2정씩 부담 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>피로 회복과 간 건강 — 꾸준히 챙겨 먹으면 컨디션 회복과 몸 상태 개선에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>뛰어난 가격 대비 성능 — 가격 부담 없이 간편하게 구입할 수 있음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -4815,7 +4809,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4823,12 +4817,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 블랙마카 60정 30일분</t>
+          <t>락피도 티니핑 아르기닌스틱 12포 12일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>락피도</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4838,28 +4832,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000141&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817122&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/pBer8sS0SwGqVuRcsAKY600000141_00_00pBer8sS0SwGqVuRcsAKY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260226/mCY81DaSP0EtG2BENK3D951817122_00_01mCY81DaSP0EtG2BENK3D.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>980</v>
+        <v>450</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>체감되는 피로 완화 — 꾸준히 먹으면 피곤함이 덜 느껴짐</t>
+          <t>아이들의 뛰어난 기호성 — 맛있고 달콤한 자두 맛이라 아이들이 거부감 없이 잘 먹음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>저렴한 영양제 — 건강 관리용으로 저렴하게 구매하기 좋음</t>
+          <t>먹기 편한 스틱 제형 — 스틱형으로 되어 있어 어디서나 간편하게 섭취시킬 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4870,7 +4864,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4878,7 +4872,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 활성엽산400 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4893,35 +4887,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000202&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251121/vNZekx45iLI6pl2rDCzm600000202_00_01vNZekx45iLI6pl2rDCzm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>630</v>
+        <v>7465</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>체감되는 어지럼증 완화 — 며칠 복용 시 어지럼증 완화 효과를 염두에 둠</t>
+          <t>우수한 가성비와 효능 — 좋은 품질 대비 가격이 저렴하여 효능 만족도가 높음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>높은 함량과 가성비 — 가격이 저렴하고 함량이 높아 만족스러움</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>부작용 없는 복용 — 별다른 부작용 없이 편하게 복용함</t>
-        </is>
-      </c>
+          <t>훌륭한 휴대성 및 보관 — 포장이 잘 되어 있어 휴대하며 매일 복용하기에 편리함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -4937,54 +4927,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 6정 6일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000280&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/1DUhwiP05cMCEONDxu7B600000280_00_011DUhwiP05cMCEONDxu7B.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>단기 복용 및 여행용 — 6일분 소량 포장이라 여행용이나 단기 섭취에 적합함</t>
+          <t>즉각적인 입안 상쾌함 — 캡슐을 터뜨리면 순간적으로 입안 전체가 시원하고 상쾌해짐</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>간편한 건강 관리 — 양이 적어 남기지 않고 간편하게 다 먹을 수 있음</t>
+          <t>외출 시 간편한 휴대 — 크기가 작아 외출할 때 들고 다니며 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>약한 지속력과 강도 — 민트 향의 강도가 엄청 강력하지 않고 지속력이 약하게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛과 식감 — 젤리 같은 묘한 말캉함과 캡슐 자체의 맛이 아쉬울 수 있음</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4992,12 +4990,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5007,47 +5005,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>889</v>
+        <v>3021</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 복용 후 피로감이 줄어들어 만족함</t>
+          <t>가성비 뛰어난 질유산균 — 비싼 여성 질 유산균을 부담 없는 가격에 꾸준히 구매 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>골고루 갖춘 성분 — 저렴한 가격에 다양한 영양 성분이 들어있음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>휴대하기 용이함 — 컴팩트하여 여행 시 챙겨 다니기 편함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 알약 크기가 커서 삼킬 때 목 넘김이 조금 힘듦</t>
-        </is>
-      </c>
+          <t>편안한 목넘김의 소형 — 알약 크기가 작고 무난하여 삼키기 쉽고 부담이 없음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5055,50 +5045,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1748</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>장 건강 개선 느낌 — 꾸준히 복용 시 장이 건강해지는 효과를 체감함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>호불호 없는 무난한 맛 — 맛이 무난하여 섭취 시 거부감이 없음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>저렴하고 손쉬운 구매 — 다이소에서 저렴한 가격에 간편히 구매 가능함</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5214,52 +5188,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>비타민D</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>혈행</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5245,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>영진약품</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5281,42 +5255,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>락피도</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
         </is>
       </c>
     </row>
@@ -5328,52 +5302,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>영진 비타민D 1000IU 아연 츄어블 12정</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>락피도 티니핑 아르기닌스틱 12포 12일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 블랙마카 60정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 활성엽산400 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 밀크씨슬 6정 6일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
     </row>
@@ -5384,13 +5358,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5399,20 +5373,18 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -5421,35 +5393,33 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>539</v>
+        <v>299</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7458</v>
+        <v>365</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2929</v>
+        <v>7010</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7006</v>
+        <v>6817</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6816</v>
+        <v>329</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>980</v>
+        <v>450</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>630</v>
+        <v>7465</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>889</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1748</v>
-      </c>
+        <v>3021</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -5459,68 +5429,60 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 천원이라는 부담 없는 가격으로 구매 가능함
-간편한 츄어블 형태 — 씹어 먹는 타입이라 간편하게 건강을 챙김</t>
+          <t>무난한 체중 관리 활용 — 다이어트 보조용으로 부담 없이 꾸준히 복용하기 무난함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격 부담이 없어 꾸준히 구매하기 좋음
-높은 매장 접근성 — 다이소에서 쉽게 구경하고 구매할 수 있음</t>
+          <t>아주 작은 알약 크기 — 정제 크기가 매우 작아 목넘김이 편하고 삼키기 쉬움
+가성비 뛰어난 고함량 — 다이소 특성상 저렴한 가격 대비 영양 함량이 우수함
+높은 브랜드 신뢰도 — 대웅제약 브랜드 제품이라 안심하고 믿고 구매함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>커피 대용으로 용이 — 일반 커피와 맛이 유사하여 부담 없이 마심
-배변 활동 도움 — 섭취 후 화장실을 잘 가도록 도와줌
-편리한 개별 포장 — 한 포씩 개별 포장되어 챙겨 먹기 간편함</t>
+          <t>훌륭한 가성비 영양제 — 저렴한 가격에 좋은 품질을 갖추어 꾸준히 구매하기 좋음
+피로 개선 체감 효과 — 복용을 중단하면 바로 피로감을 느낄 정도로 효능 체감이 확실함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>재구매율 높은 가성비 — 가격 대비 품질이 뛰어나 꾸준히 구매함
-피로 체감 효과 — 복용하지 않으면 피로감이 느껴질 정도로 도움 됨</t>
+          <t>부담 없는 저렴한 가격 — 가성비가 매우 뛰어나라 저렴하게 오메가3를 챙길 수 있음
+부담 없는 섭취 편의성 — 캡슐 섭취 시 부담이 없어 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 착한 가격에 오메가3를 구매할 수 있음
-부담 없는 알약 섭취 — 하루 2정씩 부담 없이 챙겨 먹기 좋음</t>
+          <t>소용량 포장의 휴대성 — 6일분 소용량 구성으로 단기 피로 시나 여행용으로 챙기기 좋음
+피로 회복과 간 건강 — 꾸준히 챙겨 먹으면 컨디션 회복과 몸 상태 개선에 도움이 됨
+뛰어난 가격 대비 성능 — 가격 부담 없이 간편하게 구입할 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 완화 — 꾸준히 먹으면 피곤함이 덜 느껴짐
-저렴한 영양제 — 건강 관리용으로 저렴하게 구매하기 좋음</t>
+          <t>아이들의 뛰어난 기호성 — 맛있고 달콤한 자두 맛이라 아이들이 거부감 없이 잘 먹음
+먹기 편한 스틱 제형 — 스틱형으로 되어 있어 어디서나 간편하게 섭취시킬 수 있음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 어지럼증 완화 — 며칠 복용 시 어지럼증 완화 효과를 염두에 둠
-높은 함량과 가성비 — 가격이 저렴하고 함량이 높아 만족스러움
-부작용 없는 복용 — 별다른 부작용 없이 편하게 복용함</t>
+          <t>우수한 가성비와 효능 — 좋은 품질 대비 가격이 저렴하여 효능 만족도가 높음
+훌륭한 휴대성 및 보관 — 포장이 잘 되어 있어 휴대하며 매일 복용하기에 편리함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>단기 복용 및 여행용 — 6일분 소량 포장이라 여행용이나 단기 섭취에 적합함
-간편한 건강 관리 — 양이 적어 남기지 않고 간편하게 다 먹을 수 있음</t>
+          <t>즉각적인 입안 상쾌함 — 캡슐을 터뜨리면 순간적으로 입안 전체가 시원하고 상쾌해짐
+외출 시 간편한 휴대 — 크기가 작아 외출할 때 들고 다니며 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 복용 후 피로감이 줄어들어 만족함
-골고루 갖춘 성분 — 저렴한 가격에 다양한 영양 성분이 들어있음
-휴대하기 용이함 — 컴팩트하여 여행 시 챙겨 다니기 편함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>장 건강 개선 느낌 — 꾸준히 복용 시 장이 건강해지는 효과를 체감함
-호불호 없는 무난한 맛 — 맛이 무난하여 섭취 시 거부감이 없음
-저렴하고 손쉬운 구매 — 다이소에서 저렴한 가격에 간편히 구매 가능함</t>
-        </is>
-      </c>
+          <t>가성비 뛰어난 질유산균 — 비싼 여성 질 유산균을 부담 없는 가격에 꾸준히 구매 가능함
+편안한 목넘김의 소형 — 알약 크기가 작고 무난하여 삼키기 쉽고 부담이 없음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
@@ -5528,24 +5490,29 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>카페인 민감자 주의 — 카페인 성분이 포함되어 체질에 따라 잘 맞지 않을 수 있음
+미미한 다이어트 효과 — 체감되는 뚜렷한 체중 감량 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 맛 체감 — 다이어트용이라 맛에 대한 기대는 안 하는 것이 좋음
-적은 포장 수량 — 10포 구성이라 금방 소진되어 자주 사야 함</t>
+          <t>둔감한 효능 체감 — 사람에 따라 복용 후 뚜렷한 효과를 체감하기 어려울 수 있음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 알약 크기가 커서 삼킬 때 목 넘김이 조금 힘듦</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>약한 지속력과 강도 — 민트 향의 강도가 엄청 강력하지 않고 지속력이 약하게 느껴짐
+호불호 갈리는 맛과 식감 — 젤리 같은 묘한 말캉함과 캡슐 자체의 맛이 아쉬울 수 있음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5556,52 +5523,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>1,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5726,22 +5693,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5751,16 +5718,16 @@
         <v>26.7</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5770,16 +5737,16 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5789,16 +5756,16 @@
         <v>3.3</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5808,16 +5775,16 @@
         <v>3.3</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5836,7 +5803,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5855,7 +5822,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5874,7 +5841,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5884,16 +5851,16 @@
         <v>3.3</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5907,6 +5874,25 @@
       </c>
       <c r="E11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
